--- a/worksheet.xlsx
+++ b/worksheet.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zlhte\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zlhte\sec_fmp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD325C0-F0A8-41B3-8F1E-7147B4B18A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FDA64C-40C7-48AD-A9A3-5764466DEBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17580" yWindow="2550" windowWidth="17650" windowHeight="15830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35690" yWindow="1580" windowWidth="13910" windowHeight="15830" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Full.Trajectory" sheetId="8" r:id="rId1"/>
+    <sheet name="1949.10.01" sheetId="8" r:id="rId1"/>
     <sheet name="2026.08.02" sheetId="6" r:id="rId2"/>
     <sheet name="2026.07.25" sheetId="5" r:id="rId3"/>
     <sheet name="2026.07.17" sheetId="4" r:id="rId4"/>
@@ -1078,7 +1078,7 @@
   <numFmts count="3">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1117,7 +1117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1173,8 +1173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1185,6 +1184,693 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="124">
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1222,8 +1908,27 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1245,714 +1950,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="0.0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1968,55 +1967,55 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{4B1EF7CE-7DDC-4692-862F-5C4F3B84BE7E}" name="Table16" displayName="Table16" ref="B2:H9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{4B1EF7CE-7DDC-4692-862F-5C4F3B84BE7E}" name="Table16" displayName="Table16" ref="B2:H9" totalsRowShown="0" headerRowDxfId="123" dataDxfId="122">
   <autoFilter ref="B2:H9" xr:uid="{4B1EF7CE-7DDC-4692-862F-5C4F3B84BE7E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{ADE860C1-5945-4E82-9027-D4D7DCB88D87}" name="Cohort" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{7AA42E5A-5C72-4C0E-B52D-6AAB1A28D4FE}" name="1-Jul" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{D0FB92B9-98B5-4222-96F1-247EADBBC13B}" name="5-Jul" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{AE644C28-9504-46C5-BC79-C94FE3BE06F2}" name="11-Jul" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{C1E4AE6C-4807-4C01-AE7F-B2C6FE366808}" name="19-Jul" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{3409CE35-4852-41E1-AFDB-C630003ADA86}" name="25-Jul" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{006C4307-C887-4665-84F5-D40CEF14388C}" name="2-Aug" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{ADE860C1-5945-4E82-9027-D4D7DCB88D87}" name="Cohort" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{7AA42E5A-5C72-4C0E-B52D-6AAB1A28D4FE}" name="1-Jul" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{D0FB92B9-98B5-4222-96F1-247EADBBC13B}" name="5-Jul" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{AE644C28-9504-46C5-BC79-C94FE3BE06F2}" name="11-Jul" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{C1E4AE6C-4807-4C01-AE7F-B2C6FE366808}" name="19-Jul" dataDxfId="117"/>
+    <tableColumn id="6" xr3:uid="{3409CE35-4852-41E1-AFDB-C630003ADA86}" name="25-Jul" dataDxfId="116"/>
+    <tableColumn id="7" xr3:uid="{006C4307-C887-4665-84F5-D40CEF14388C}" name="2-Aug" dataDxfId="115"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F5855836-0D81-4482-AF29-D8BCC9C6FF3F}" name="Table7" displayName="Table7" ref="B2:I32" totalsRowShown="0" headerRowDxfId="68" dataDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F5855836-0D81-4482-AF29-D8BCC9C6FF3F}" name="Table7" displayName="Table7" ref="B2:I32" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="B2:I32" xr:uid="{F5855836-0D81-4482-AF29-D8BCC9C6FF3F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4AC4C1CA-53E7-48BF-BF7F-FA639C2A6B76}" name="Ticker" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{178CA632-EB06-44BC-8B20-47EED196DBC2}" name="Purchase date" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{0305448B-C090-44C5-91F1-B4FDE2514FCB}" name="IBKR current market value" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{9AD02E40-2778-4311-8F02-CBC47AF41134}" name="Cost basis + quantity" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{935C0CDA-AD33-4D3C-84C4-C6AB8111E89E}" name="Return since purchase" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{DD45E734-36EA-434C-835E-39DCBD580048}" name="S&amp;P 500 / SPY return" dataDxfId="72"/>
-    <tableColumn id="7" xr3:uid="{F43F72D5-59E6-49ED-8F5B-38978F7FA8EE}" name="Excess vs S&amp;P 500" dataDxfId="71"/>
-    <tableColumn id="8" xr3:uid="{6BEF8874-3AE7-447C-BF82-DE881F8203C4}" name="Calendar days held" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{4AC4C1CA-53E7-48BF-BF7F-FA639C2A6B76}" name="Ticker" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{178CA632-EB06-44BC-8B20-47EED196DBC2}" name="Purchase date" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{0305448B-C090-44C5-91F1-B4FDE2514FCB}" name="IBKR current market value" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{9AD02E40-2778-4311-8F02-CBC47AF41134}" name="Cost basis + quantity" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{935C0CDA-AD33-4D3C-84C4-C6AB8111E89E}" name="Return since purchase" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{DD45E734-36EA-434C-835E-39DCBD580048}" name="S&amp;P 500 / SPY return" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{F43F72D5-59E6-49ED-8F5B-38978F7FA8EE}" name="Excess vs S&amp;P 500" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{6BEF8874-3AE7-447C-BF82-DE881F8203C4}" name="Calendar days held" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C5D05F0E-EB2B-4F5A-B1EB-51A0B8FF555F}" name="Table8" displayName="Table8" ref="B47:G77" totalsRowShown="0" headerRowDxfId="60" dataDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C5D05F0E-EB2B-4F5A-B1EB-51A0B8FF555F}" name="Table8" displayName="Table8" ref="B47:G77" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="B47:G77" xr:uid="{C5D05F0E-EB2B-4F5A-B1EB-51A0B8FF555F}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D590492E-65F3-4532-AF2E-2F19EE5292BA}" name="Ticker" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{0961A36D-E8D4-487C-BB25-3A0008F891AE}" name="Purchase date" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{EC1F6FBF-0B1E-4BB2-9A91-7EC85E73C3E6}" name="Best return achieved" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{92E5AB19-B298-4308-B902-D766DEE2FCBB}" name="Calendar days to peak" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{9908057F-3547-4F71-BCA5-EFB8C4A0444E}" name="Worst return during holding period" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{FD06B0FE-2447-4BFD-9100-C697D9AA1B15}" name="Calendar days to trough" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{D590492E-65F3-4532-AF2E-2F19EE5292BA}" name="Ticker" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{0961A36D-E8D4-487C-BB25-3A0008F891AE}" name="Purchase date" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{EC1F6FBF-0B1E-4BB2-9A91-7EC85E73C3E6}" name="Best return achieved" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{92E5AB19-B298-4308-B902-D766DEE2FCBB}" name="Calendar days to peak" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{9908057F-3547-4F71-BCA5-EFB8C4A0444E}" name="Worst return during holding period" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{FD06B0FE-2447-4BFD-9100-C697D9AA1B15}" name="Calendar days to trough" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF4C8E37-B3D0-4332-9961-605C5C4BCD9C}" name="Table510" displayName="Table510" ref="A35:H44" totalsRowShown="0" headerRowDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF4C8E37-B3D0-4332-9961-605C5C4BCD9C}" name="Table510" displayName="Table510" ref="A35:H44" totalsRowShown="0" headerRowDxfId="28">
   <autoFilter ref="A35:H44" xr:uid="{EF4C8E37-B3D0-4332-9961-605C5C4BCD9C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{65660A6C-48D6-4730-9758-2827F2642AB2}" name="Purchase cohort"/>
@@ -2033,141 +2032,141 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1EFD31B7-92EC-435F-9541-A3F767D18462}" name="Table3" displayName="Table3" ref="B2:I26" totalsRowShown="0" headerRowDxfId="96" dataDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1EFD31B7-92EC-435F-9541-A3F767D18462}" name="Table3" displayName="Table3" ref="B2:I26" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="B2:I26" xr:uid="{1EFD31B7-92EC-435F-9541-A3F767D18462}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6E1EB0D0-813E-4819-99B1-A4F898835DFB}" name="Ticker" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{15C516B1-673B-43EA-AE65-616C6E8D0719}" name="Purchase date" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{8F01E83E-AE03-4B82-94DD-8D3AC26E3322}" name="IBKR current market value" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{E2159248-D44B-44F9-AD67-A4415B722AA0}" name="Cost basis + quantity" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{653B3875-8365-44F2-A1B0-29A9A3C19C22}" name="Return since purchase" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{FB048E91-60FA-4497-99B9-E10305B6FAAD}" name="S&amp;P 500 / SPY return" dataDxfId="100"/>
-    <tableColumn id="7" xr3:uid="{1D886A63-4705-4C60-A235-051512734BC3}" name="Excess vs S&amp;P 500" dataDxfId="99"/>
-    <tableColumn id="8" xr3:uid="{645161C0-0C74-4F78-9D47-E21ED05B88B1}" name="Calendar days held" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{6E1EB0D0-813E-4819-99B1-A4F898835DFB}" name="Ticker" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{15C516B1-673B-43EA-AE65-616C6E8D0719}" name="Purchase date" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{8F01E83E-AE03-4B82-94DD-8D3AC26E3322}" name="IBKR current market value" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{E2159248-D44B-44F9-AD67-A4415B722AA0}" name="Cost basis + quantity" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{653B3875-8365-44F2-A1B0-29A9A3C19C22}" name="Return since purchase" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{FB048E91-60FA-4497-99B9-E10305B6FAAD}" name="S&amp;P 500 / SPY return" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{1D886A63-4705-4C60-A235-051512734BC3}" name="Excess vs S&amp;P 500" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{645161C0-0C74-4F78-9D47-E21ED05B88B1}" name="Calendar days held" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{873955EE-78A8-4126-B3EB-1C9B75AA95F8}" name="Table5" displayName="Table5" ref="A29:H37" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{873955EE-78A8-4126-B3EB-1C9B75AA95F8}" name="Table5" displayName="Table5" ref="A29:H37" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A29:H37" xr:uid="{873955EE-78A8-4126-B3EB-1C9B75AA95F8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{862E4EE9-08FF-4809-8072-713D3A5693EF}" name="Purchase cohort" dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{B7EA62A4-CDA7-475B-8E6D-2261BF1EB08A}" name="N" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{367CE14C-C481-4E96-BE77-CA364C002611}" name="Cost" dataDxfId="84"/>
-    <tableColumn id="4" xr3:uid="{FDFEE0DE-4C38-4562-8FA9-13258ED6B9E5}" name="Value" dataDxfId="83"/>
-    <tableColumn id="5" xr3:uid="{CB67300C-BDF2-476B-81E8-4F66EC942ABC}" name="P/L$" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{38343DC3-85AC-4171-91F0-11011EDB5B1E}" name="Return" dataDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{11947081-29D9-4312-84FB-10D1D007C175}" name="SPY, cost-weighted" dataDxfId="80"/>
-    <tableColumn id="8" xr3:uid="{877D3FA6-FE1A-4D0F-ABAA-A599B2ECA574}" name="Excess" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{862E4EE9-08FF-4809-8072-713D3A5693EF}" name="Purchase cohort" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{B7EA62A4-CDA7-475B-8E6D-2261BF1EB08A}" name="N" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{367CE14C-C481-4E96-BE77-CA364C002611}" name="Cost" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{FDFEE0DE-4C38-4562-8FA9-13258ED6B9E5}" name="Value" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{CB67300C-BDF2-476B-81E8-4F66EC942ABC}" name="P/L$" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{38343DC3-85AC-4171-91F0-11011EDB5B1E}" name="Return" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{11947081-29D9-4312-84FB-10D1D007C175}" name="SPY, cost-weighted" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{877D3FA6-FE1A-4D0F-ABAA-A599B2ECA574}" name="Excess" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ABF8D4E4-0DDD-4D7A-8398-5FF096CC01D8}" name="Table6" displayName="Table6" ref="B40:G64" totalsRowShown="0" headerRowDxfId="78" dataDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ABF8D4E4-0DDD-4D7A-8398-5FF096CC01D8}" name="Table6" displayName="Table6" ref="B40:G64" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="B40:G64" xr:uid="{ABF8D4E4-0DDD-4D7A-8398-5FF096CC01D8}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9F2A07CD-2534-4CDA-81CD-639ADC44E478}" name="Ticker" dataDxfId="95"/>
-    <tableColumn id="2" xr3:uid="{E455EA5F-264F-45CA-AD18-CD9255F410D8}" name="Purchase date" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{8686EDE0-7542-4FC9-AD2B-F6344FE61B8E}" name="Best return achieved" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{1F56293E-CA91-4E75-9EBA-F48F3379844A}" name="Calendar days to peak" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{86AECBE6-98E8-44DC-B9CC-17E75B58D38B}" name="Worst return during holding period" dataDxfId="91"/>
-    <tableColumn id="6" xr3:uid="{5322463C-2CFD-4D21-BF1D-3A48385CC790}" name="Calendar days to trough" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{9F2A07CD-2534-4CDA-81CD-639ADC44E478}" name="Ticker" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E455EA5F-264F-45CA-AD18-CD9255F410D8}" name="Purchase date" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{8686EDE0-7542-4FC9-AD2B-F6344FE61B8E}" name="Best return achieved" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{1F56293E-CA91-4E75-9EBA-F48F3379844A}" name="Calendar days to peak" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{86AECBE6-98E8-44DC-B9CC-17E75B58D38B}" name="Worst return during holding period" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{5322463C-2CFD-4D21-BF1D-3A48385CC790}" name="Calendar days to trough" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{082C7577-0157-40B5-89D1-82BE8E3EECB7}" name="Table17" displayName="Table17" ref="B21:H23" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{082C7577-0157-40B5-89D1-82BE8E3EECB7}" name="Table17" displayName="Table17" ref="B21:H23" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
   <autoFilter ref="B21:H23" xr:uid="{082C7577-0157-40B5-89D1-82BE8E3EECB7}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{778DD026-C611-48E3-9E00-52A94872D5AC}" name="Column1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{2D407C54-0AD2-4A9A-ADA3-D01F3514EB42}" name="1-Jul" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{4EB1B342-1451-40AB-8802-02DC674CB8B2}" name="5-Jul" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{9FFA3685-C418-4B7C-AD1F-52AB2F9CC9B1}" name="11-Jul" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{67708D54-BBB7-4286-A2AE-22A0945337C3}" name="19-Jul" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{6F4145EE-6030-4CE6-ACAA-D9C4F527FB7F}" name="25-Jul" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{285C6FF2-70D2-4C07-90A1-C39BDEBD4B2C}" name="2-Aug" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{778DD026-C611-48E3-9E00-52A94872D5AC}" name="Column1" dataDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{2D407C54-0AD2-4A9A-ADA3-D01F3514EB42}" name="1-Jul" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{4EB1B342-1451-40AB-8802-02DC674CB8B2}" name="5-Jul" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{9FFA3685-C418-4B7C-AD1F-52AB2F9CC9B1}" name="11-Jul" dataDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{67708D54-BBB7-4286-A2AE-22A0945337C3}" name="19-Jul" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{6F4145EE-6030-4CE6-ACAA-D9C4F527FB7F}" name="25-Jul" dataDxfId="107"/>
+    <tableColumn id="7" xr3:uid="{285C6FF2-70D2-4C07-90A1-C39BDEBD4B2C}" name="2-Aug" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{112BA892-A153-40B9-8727-0549D8A86BD6}" name="Table1" displayName="Table1" ref="B48:G78" totalsRowShown="0" headerRowDxfId="116" dataDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{112BA892-A153-40B9-8727-0549D8A86BD6}" name="Table1" displayName="Table1" ref="B48:G78" totalsRowShown="0" headerRowDxfId="105" dataDxfId="104">
   <autoFilter ref="B48:G78" xr:uid="{112BA892-A153-40B9-8727-0549D8A86BD6}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6FD51C95-DD78-4B2F-A21D-C0B1EEAC6B99}" name="Ticker" dataDxfId="123"/>
-    <tableColumn id="2" xr3:uid="{C8BC3673-A2C5-4504-882E-959BB227580E}" name="Purchase date" dataDxfId="122"/>
-    <tableColumn id="3" xr3:uid="{411B94B7-4B6F-4344-B7F3-753E7B1393DC}" name="Best return achieved" dataDxfId="121"/>
-    <tableColumn id="4" xr3:uid="{96C5B0C3-54DC-49BF-9CB8-29958D8B364B}" name="Calendar days to peak" dataDxfId="120"/>
-    <tableColumn id="5" xr3:uid="{0AA7F056-1D57-4088-A6E5-277EE510704F}" name="Worst return during holding period" dataDxfId="119"/>
-    <tableColumn id="6" xr3:uid="{D27062B7-E0FD-4062-B3EE-3236F8433E5B}" name="Calendar days to trough" dataDxfId="118"/>
+    <tableColumn id="1" xr3:uid="{6FD51C95-DD78-4B2F-A21D-C0B1EEAC6B99}" name="Ticker" dataDxfId="103"/>
+    <tableColumn id="2" xr3:uid="{C8BC3673-A2C5-4504-882E-959BB227580E}" name="Purchase date" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{411B94B7-4B6F-4344-B7F3-753E7B1393DC}" name="Best return achieved" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{96C5B0C3-54DC-49BF-9CB8-29958D8B364B}" name="Calendar days to peak" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{0AA7F056-1D57-4088-A6E5-277EE510704F}" name="Worst return during holding period" dataDxfId="99"/>
+    <tableColumn id="6" xr3:uid="{D27062B7-E0FD-4062-B3EE-3236F8433E5B}" name="Calendar days to trough" dataDxfId="98"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{71F86AC9-7EC8-4B85-88F6-725C3C2205CD}" name="Table2" displayName="Table2" ref="B2:I32" totalsRowShown="0" headerRowDxfId="106" dataDxfId="107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{71F86AC9-7EC8-4B85-88F6-725C3C2205CD}" name="Table2" displayName="Table2" ref="B2:I32" totalsRowShown="0" headerRowDxfId="97" dataDxfId="96">
   <autoFilter ref="B2:I32" xr:uid="{71F86AC9-7EC8-4B85-88F6-725C3C2205CD}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4329B509-85E2-4EAD-AA3C-ECD35D643E4A}" name="Ticker" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{2E749932-270F-4E46-9CD0-C5D8D8C5C883}" name="Purchase date" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{D4A8B57B-2F7B-4984-A2D2-F3166F576405}" name="IBKR current market value" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{6C02D030-DA4B-4CED-B032-1EA8FBF2A201}" name="Cost basis + quantity" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{6D588F39-D215-4D02-B8FA-866BDA2873B1}" name="Return since purchase" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{B3E1D062-FCBD-440F-A553-9868EDBFF32D}" name="S&amp;P 500 / SPY return" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{23413103-2056-422A-9A06-CD307F0FAE2D}" name="Excess vs S&amp;P 500" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{1F328FEE-BC04-401E-9576-117B8930D1D0}" name="Calendar days held" dataDxfId="108"/>
+    <tableColumn id="1" xr3:uid="{4329B509-85E2-4EAD-AA3C-ECD35D643E4A}" name="Ticker" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{2E749932-270F-4E46-9CD0-C5D8D8C5C883}" name="Purchase date" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{D4A8B57B-2F7B-4984-A2D2-F3166F576405}" name="IBKR current market value" dataDxfId="93"/>
+    <tableColumn id="4" xr3:uid="{6C02D030-DA4B-4CED-B032-1EA8FBF2A201}" name="Cost basis + quantity" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{6D588F39-D215-4D02-B8FA-866BDA2873B1}" name="Return since purchase" dataDxfId="91"/>
+    <tableColumn id="6" xr3:uid="{B3E1D062-FCBD-440F-A553-9868EDBFF32D}" name="S&amp;P 500 / SPY return" dataDxfId="90"/>
+    <tableColumn id="7" xr3:uid="{23413103-2056-422A-9A06-CD307F0FAE2D}" name="Excess vs S&amp;P 500" dataDxfId="89"/>
+    <tableColumn id="8" xr3:uid="{1F328FEE-BC04-401E-9576-117B8930D1D0}" name="Calendar days held" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{148683F5-F4DE-4462-A2E8-3D634021F1FE}" name="Table15" displayName="Table15" ref="A35:H44" totalsRowShown="0" headerRowDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{148683F5-F4DE-4462-A2E8-3D634021F1FE}" name="Table15" displayName="Table15" ref="A35:H44" totalsRowShown="0" headerRowDxfId="87">
   <autoFilter ref="A35:H44" xr:uid="{148683F5-F4DE-4462-A2E8-3D634021F1FE}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{26E5A63C-A515-4037-91A2-A66AF18313B8}" name="Purchase cohort" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{33DBA537-701A-4060-981C-E1056CDE88ED}" name="N" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{16A43168-7974-413A-8D24-300EE3AF83BD}" name="Cost" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{A9F98E78-9D46-4B8E-948E-DB37864B6B98}" name="Value" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{EF927CEB-4328-4B3E-8AD5-7C85A2AA68DA}" name="P/L$" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{2CE49388-B629-433E-BF24-3D12C142E02B}" name="Return" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{95993E38-B48C-4A8F-921B-AC3CF30157D6}" name="SPY, cost-weighted" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{04855F8B-297F-495A-9649-72283C711181}" name="Excess" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{26E5A63C-A515-4037-91A2-A66AF18313B8}" name="Purchase cohort" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{33DBA537-701A-4060-981C-E1056CDE88ED}" name="N" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{16A43168-7974-413A-8D24-300EE3AF83BD}" name="Cost" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{A9F98E78-9D46-4B8E-948E-DB37864B6B98}" name="Value" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{EF927CEB-4328-4B3E-8AD5-7C85A2AA68DA}" name="P/L$" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{2CE49388-B629-433E-BF24-3D12C142E02B}" name="Return" dataDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{95993E38-B48C-4A8F-921B-AC3CF30157D6}" name="SPY, cost-weighted" dataDxfId="80"/>
+    <tableColumn id="8" xr3:uid="{04855F8B-297F-495A-9649-72283C711181}" name="Excess" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{6768034F-262A-404F-922D-D174008EBAFD}" name="Table12" displayName="Table12" ref="B2:I32" totalsRowShown="0" headerRowDxfId="29" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{6768034F-262A-404F-922D-D174008EBAFD}" name="Table12" displayName="Table12" ref="B2:I32" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77">
   <autoFilter ref="B2:I32" xr:uid="{6768034F-262A-404F-922D-D174008EBAFD}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7131125A-F229-499D-BDA9-EB5277D89937}" name="Ticker" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{536FBDBB-290A-4402-B998-581AA05C2DAD}" name="Purchase date" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{55ECC7CE-42DC-4D58-8F76-8D1610F33964}" name="IBKR current market value" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{52229082-3BC6-4299-8731-A40022A22816}" name="Cost basis + quantity" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{7DA0EF66-A6A8-47D4-A78C-A89EF84AFE0C}" name="Return since purchase" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{800BDBE7-E6EC-4992-9DA9-21A4EC529090}" name="S&amp;P 500 / SPY return" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{BD6217E0-615A-47B5-ABAE-D97FD8DD19C4}" name="Excess vs S&amp;P 500" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{61B719C5-1904-4B24-8FCB-123E3D51145B}" name="Calendar days held" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{7131125A-F229-499D-BDA9-EB5277D89937}" name="Ticker" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{536FBDBB-290A-4402-B998-581AA05C2DAD}" name="Purchase date" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{55ECC7CE-42DC-4D58-8F76-8D1610F33964}" name="IBKR current market value" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{52229082-3BC6-4299-8731-A40022A22816}" name="Cost basis + quantity" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{7DA0EF66-A6A8-47D4-A78C-A89EF84AFE0C}" name="Return since purchase" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{800BDBE7-E6EC-4992-9DA9-21A4EC529090}" name="S&amp;P 500 / SPY return" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{BD6217E0-615A-47B5-ABAE-D97FD8DD19C4}" name="Excess vs S&amp;P 500" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{61B719C5-1904-4B24-8FCB-123E3D51145B}" name="Calendar days held" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{93A58E32-FBA1-4205-B32E-9643182257DC}" name="Table13" displayName="Table13" ref="A35:H44" totalsRowShown="0" headerRowDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{93A58E32-FBA1-4205-B32E-9643182257DC}" name="Table13" displayName="Table13" ref="A35:H44" totalsRowShown="0" headerRowDxfId="68">
   <autoFilter ref="A35:H44" xr:uid="{93A58E32-FBA1-4205-B32E-9643182257DC}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1634BC2D-61E0-4206-BFF1-F0232A376221}" name="Purchase cohort" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{1634BC2D-61E0-4206-BFF1-F0232A376221}" name="Purchase cohort" dataDxfId="67"/>
     <tableColumn id="2" xr3:uid="{B5706824-9BB7-4FB1-9003-B07D9476C6D2}" name="N"/>
     <tableColumn id="3" xr3:uid="{CBA5E65C-70CF-4463-AE29-E9B9BA35EE8D}" name="Cost"/>
     <tableColumn id="4" xr3:uid="{731C3EFD-3AD1-45CF-A07F-9C4D3F85E91C}" name="Value"/>
@@ -2181,34 +2180,34 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E6A337FE-FCB0-4762-9E05-B75B8DF55E91}" name="Table10" displayName="Table10" ref="B2:I32" totalsRowShown="0" headerRowDxfId="49" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E6A337FE-FCB0-4762-9E05-B75B8DF55E91}" name="Table10" displayName="Table10" ref="B2:I32" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="B2:I32" xr:uid="{E6A337FE-FCB0-4762-9E05-B75B8DF55E91}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{322E06A8-9D07-4870-A1F1-BF72D0389716}" name="Ticker" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{3333F0C0-F252-4A53-A40A-56D328C6AA67}" name="Purchase date" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{85FEB9AD-32BD-4DD0-9F1B-13F66A6D0C94}" name="IBKR current market value" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{7FAF41F7-50F0-41E8-9EBA-D328FFAFB23B}" name="Cost basis + quantity" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{83AEA444-3FC8-415D-9F49-BD912C2D5541}" name="Return since purchase" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{162DB293-C65B-4879-A266-365C3A72F2B4}" name="S&amp;P 500 / SPY return" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{013F4231-5A00-4283-A430-4217DE5E9031}" name="Excess vs S&amp;P 500" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{1B1E4488-80AA-4FD2-A61E-5FE81BBB24EA}" name="Calendar days held" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{322E06A8-9D07-4870-A1F1-BF72D0389716}" name="Ticker" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{3333F0C0-F252-4A53-A40A-56D328C6AA67}" name="Purchase date" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{85FEB9AD-32BD-4DD0-9F1B-13F66A6D0C94}" name="IBKR current market value" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{7FAF41F7-50F0-41E8-9EBA-D328FFAFB23B}" name="Cost basis + quantity" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{83AEA444-3FC8-415D-9F49-BD912C2D5541}" name="Return since purchase" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{162DB293-C65B-4879-A266-365C3A72F2B4}" name="S&amp;P 500 / SPY return" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{013F4231-5A00-4283-A430-4217DE5E9031}" name="Excess vs S&amp;P 500" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{1B1E4488-80AA-4FD2-A61E-5FE81BBB24EA}" name="Calendar days held" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4ADD85DA-36E1-4710-ABB2-E61097B1894C}" name="Table11" displayName="Table11" ref="A35:H44" totalsRowShown="0" headerRowDxfId="39" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4ADD85DA-36E1-4710-ABB2-E61097B1894C}" name="Table11" displayName="Table11" ref="A35:H44" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A35:H44" xr:uid="{4ADD85DA-36E1-4710-ABB2-E61097B1894C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{56517BA2-5289-4B6A-89B4-FDF25AD3AEB7}" name="Purchase cohort" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{68F268C5-839B-4318-A6FD-BFB4FC72E46E}" name="N" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{AC422341-7EBB-4CD4-A3E0-0315C2C16FE6}" name="Cost" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{ACECCFC2-6AD6-4BF6-B755-2B9D30A6F048}" name="Value" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{B21BFD63-B23E-4967-83A3-6EB6941D929D}" name="P/L$" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{A1B45AA2-77B8-4691-93A0-BBD5783DBECE}" name="Return" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{7D7A8329-C139-4554-AF12-0396F33427BE}" name="SPY, cost-weighted" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{C3E9928C-F7A0-4A10-94E0-3725CE425DFB}" name="Excess" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{56517BA2-5289-4B6A-89B4-FDF25AD3AEB7}" name="Purchase cohort" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{68F268C5-839B-4318-A6FD-BFB4FC72E46E}" name="N" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{AC422341-7EBB-4CD4-A3E0-0315C2C16FE6}" name="Cost" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{ACECCFC2-6AD6-4BF6-B755-2B9D30A6F048}" name="Value" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{B21BFD63-B23E-4967-83A3-6EB6941D929D}" name="P/L$" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{A1B45AA2-77B8-4691-93A0-BBD5783DBECE}" name="Return" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{7D7A8329-C139-4554-AF12-0396F33427BE}" name="SPY, cost-weighted" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{C3E9928C-F7A0-4A10-94E0-3725CE425DFB}" name="Excess" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2487,22 +2486,22 @@
       <c r="B2" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>335</v>
       </c>
     </row>
@@ -2525,7 +2524,7 @@
       <c r="G3" s="2">
         <v>3.5</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="19">
         <v>4</v>
       </c>
     </row>
@@ -2548,7 +2547,7 @@
       <c r="G4" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>310</v>
       </c>
     </row>
@@ -2571,7 +2570,7 @@
       <c r="G5" s="2">
         <v>7.1</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="19">
         <v>6.5</v>
       </c>
     </row>
@@ -2594,7 +2593,7 @@
       <c r="G6" s="2">
         <v>53.4</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <v>64.099999999999994</v>
       </c>
     </row>
@@ -2617,7 +2616,7 @@
       <c r="G7" s="2">
         <v>1.8</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="19">
         <v>5</v>
       </c>
     </row>
@@ -2640,7 +2639,7 @@
       <c r="G8" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>318</v>
       </c>
     </row>
@@ -2663,7 +2662,7 @@
       <c r="G9" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2671,22 +2670,22 @@
       <c r="B21" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="20" t="s">
         <v>335</v>
       </c>
     </row>
@@ -3583,7 +3582,7 @@
       <c r="F34" s="7"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:8" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>231</v>
       </c>
@@ -7038,7 +7037,7 @@
       <c r="F33" s="7"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="35" spans="1:8" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>231</v>
       </c>
